--- a/output/full_scan/batch_seq6_2026-09-04.xlsx
+++ b/output/full_scan/batch_seq6_2026-09-04.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>943.9372232911188</v>
+        <v>1208.937223291119</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>49.2</v>
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.78164486298286</v>
+        <v>59.78164487350576</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>22.71115770333063</v>
@@ -561,40 +561,40 @@
         <v>1.421481379752759</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0547500746106011</v>
+        <v>0.0547500745438229</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6275</v>
+        <v>6271</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>831.439947820573</v>
+        <v>991.8565980599144</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48.15</v>
+        <v>237</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>62.80921034891337</v>
+        <v>65.06619760166635</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.2247819125003</v>
+        <v>17.91906440668587</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.209165467554423</v>
+        <v>3.099151064957697</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3542234701925673</v>
+        <v>4.336466066974976</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6271</v>
+        <v>6214</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>821.8565980599143</v>
+        <v>973.0927307312414</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>237</v>
+        <v>185.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.06619756893318</v>
+        <v>75.88368626991885</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.91906438543139</v>
+        <v>39.52424383911881</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.099151064957697</v>
+        <v>0.4561730871534266</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4.336466067356558</v>
+        <v>-0.2423677059445328</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6426</v>
+        <v>6275</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>799.9381745317864</v>
+        <v>971.439947820573</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>269.5</v>
+        <v>48.15</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.0876262882048</v>
+        <v>62.80921035095614</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.58954197395006</v>
+        <v>26.22478190386564</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.387506655302993</v>
+        <v>4.209165467554423</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7039467094174405</v>
+        <v>0.3542234702116476</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6168</v>
+        <v>6290</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>787.946709526074</v>
+        <v>943.223597652688</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29.05</v>
+        <v>270</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.67072610906423</v>
+        <v>63.48976711933514</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>21.19988601205508</v>
+        <v>25.84741855981751</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.4269115725369</v>
+        <v>1.422359765268817</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2507422098165607</v>
+        <v>5.685542825820691</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>786.9460754732854</v>
+        <v>926.946075473292</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>516</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>54.68505178329094</v>
+        <v>54.68505180790859</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10.2301939409595</v>
+        <v>10.23019396306784</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.958464311376473</v>
@@ -829,37 +829,37 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.546449316122879</v>
+        <v>2.546449315264291</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6290</v>
+        <v>6173</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>773.2235976526881</v>
+        <v>915.5492687341653</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>270</v>
+        <v>260.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.48976709154629</v>
+        <v>62.3845583305651</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.84741862596047</v>
+        <v>22.2172243901894</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.422359765268817</v>
+        <v>1.06267626558943</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>5.685542826488464</v>
+        <v>6.334266586854514</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6173</v>
+        <v>6426</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>745.5492687341653</v>
+        <v>914.9381745317864</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>260.5</v>
+        <v>269.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.38455832843856</v>
+        <v>65.0876263166037</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.21722445862049</v>
+        <v>35.58954199846925</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.06267626558943</v>
+        <v>1.387506655302993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>6.33426658686406</v>
+        <v>0.7039467090358471</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>743.5507875363512</v>
+        <v>911.0654043716949</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>200</v>
+        <v>84.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.24744110615881</v>
+        <v>66.16163868722202</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.03255546415242</v>
+        <v>37.29355229020781</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6019005127739847</v>
+        <v>2.017633231763102</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.673901905188557</v>
+        <v>1.264069221581451</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6214</v>
+        <v>6168</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>743.0927307312414</v>
+        <v>902.946709526074</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>185.5</v>
+        <v>29.05</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>75.88368630171229</v>
+        <v>62.67072611158049</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.52424380489713</v>
+        <v>21.19988594022383</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4561730871534266</v>
+        <v>2.4269115725369</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.2423677059445328</v>
+        <v>0.2507422098165607</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6224</v>
+        <v>6291</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>701.0654043716949</v>
+        <v>873.0245902184433</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>84.8</v>
+        <v>456.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.16163867032628</v>
+        <v>63.22817403667011</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>37.29355236883883</v>
+        <v>19.41615556184973</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.017633231763102</v>
+        <v>2.637798930333683</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.264069221705478</v>
+        <v>10.58054981751461</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6263</v>
+        <v>6278</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>687.221005985255</v>
+        <v>848.5507875363512</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>169.5</v>
+        <v>200</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,29 +1135,29 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.86172770085612</v>
+        <v>60.2474411411759</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.02894406374945</v>
+        <v>21.03255555604129</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.023356078160656</v>
+        <v>0.6019005127739847</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.7692307293615896</v>
+        <v>1.673901904711584</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>687.0668483375185</v>
+        <v>827.0668483375186</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>42.25</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.95791480415636</v>
+        <v>65.95791482097604</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>39.43649482698012</v>
+        <v>39.43649486671095</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.9256480562791932</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.388410173575483</v>
+        <v>0.3884101735659429</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6291</v>
+        <v>6263</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>673.0245902184432</v>
+        <v>802.221005985255</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>456.5</v>
+        <v>169.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.22817403263792</v>
+        <v>60.86172770085612</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>19.41615556184975</v>
+        <v>18.02894408574297</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.637798930333683</v>
+        <v>1.023356078160656</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>10.58054981757183</v>
+        <v>0.7692307295523859</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>657.7476035995217</v>
+        <v>762.7476035995217</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>517</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.27375309666204</v>
+        <v>58.27375311430711</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.61228660500997</v>
+        <v>28.61228661245029</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.8505184265869061</v>
@@ -1306,37 +1306,37 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-5.877425980284762</v>
+        <v>-5.877425980456472</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6187</v>
+        <v>6272</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>627.452331510104</v>
+        <v>749</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1305</v>
+        <v>29.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,29 +1347,29 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.96564543629677</v>
+        <v>69.33622279631975</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.09194881002089</v>
+        <v>41.31621605631167</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5082303454780066</v>
+        <v>5.149251014809829</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-4.327185557150685</v>
+        <v>0.855517598249522</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>608.0318854582789</v>
+        <v>723.0318854582789</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>60</v>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>65.6806288117893</v>
+        <v>65.68062879498662</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46.18203733412607</v>
+        <v>46.18203730121614</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.3180710954216045</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.7928451682986903</v>
+        <v>-0.7928451682700715</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6416</v>
+        <v>6209</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>572.2978961004479</v>
+        <v>695.5887357088585</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>100.5</v>
+        <v>81.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53.46046860750432</v>
+        <v>61.1956392062718</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13.1347324074259</v>
+        <v>19.68498736055253</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8713115151236965</v>
+        <v>1.014651369482456</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,11 +1471,11 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.3014324216718009</v>
+        <v>1.435386915023712</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>567.2644948227897</v>
+        <v>682.2644948227899</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>315</v>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.84292401604004</v>
+        <v>53.84292404081717</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.83774379099394</v>
+        <v>13.83774389915076</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.89042475604832</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.864043893776333</v>
+        <v>1.864043892536176</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6207</v>
+        <v>6217</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>558.8115294721562</v>
+        <v>653.8787019276429</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>111</v>
+        <v>188.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.14347090827597</v>
+        <v>58.08629123155443</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10.46229752820941</v>
+        <v>18.58329486538591</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.281005478993907</v>
+        <v>1.937681443369062</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.295378268961894</v>
+        <v>5.902063493936117</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6435</v>
+        <v>6446</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>558.1364248151053</v>
+        <v>638.3942849975497</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>246</v>
+        <v>1310</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>43.59652880606541</v>
+        <v>45.98292450109958</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.66106396129482</v>
+        <v>27.20104968871096</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3710273498593003</v>
+        <v>0.7895212834361595</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.01963697329656</v>
+        <v>-27.06100867983485</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6272</v>
+        <v>6423</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>549</v>
+        <v>634.1355088797334</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>29.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>69.33622256517083</v>
+        <v>64.30457693868098</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>41.31621593487035</v>
+        <v>20.54190927130911</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.149251014809829</v>
+        <v>0.5826623741650099</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.8555175986501906</v>
+        <v>0.5488475614439037</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6209</v>
+        <v>6438</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>525.5887357088585</v>
+        <v>631.9959178147509</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>81.5</v>
+        <v>156.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.19563919439113</v>
+        <v>59.34763742398784</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19.68498736055254</v>
+        <v>17.50470850491305</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.014651369482456</v>
+        <v>1.009644551929326</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.43538691509048</v>
+        <v>1.50932464170377</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6170</v>
+        <v>6161</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>510.9712711696054</v>
+        <v>628.6127924762629</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>48.45</v>
+        <v>51.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.74244214521361</v>
+        <v>52.68820442684674</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.12499580885695</v>
+        <v>9.153623903504458</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9384612786231096</v>
+        <v>0.6471164566813904</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1024074515611215</v>
+        <v>0.0744418688146514</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6472</v>
+        <v>6187</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>504.1298172700867</v>
+        <v>627.5207807278473</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>416</v>
+        <v>1305</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.72050961001558</v>
+        <v>54.96564544000028</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.20214842750459</v>
+        <v>22.09194875410746</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2685511841744173</v>
+        <v>0.5119547846367094</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-3.683574726939933</v>
+        <v>-4.327185557532175</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6438</v>
+        <v>6183</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>501.9959178147498</v>
+        <v>622.9328337392931</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>156.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.34763730992054</v>
+        <v>45.51284975352493</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>17.50470847442941</v>
+        <v>25.72547007275673</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.009644551929326</v>
+        <v>0.4119734973970658</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.509324642562356</v>
+        <v>-0.3322531837476546</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6285</v>
+        <v>6202</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>499.9631336046217</v>
+        <v>617.5985980523867</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>243.5</v>
+        <v>58.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>50.38497437703115</v>
+        <v>50.28467345953963</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.29558222206857</v>
+        <v>10.43151111020755</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7128875990043481</v>
+        <v>0.6337651143190621</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5882009212230488</v>
+        <v>0.0662462744208827</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6202</v>
+        <v>6204</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>497.5985980523866</v>
+        <v>614.0938269924886</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>58.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.28467342639147</v>
+        <v>58.8777051271362</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10.43151112166064</v>
+        <v>18.59314434230945</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6337651143190621</v>
+        <v>1.087966141129599</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.06624627455444219</v>
+        <v>1.129728731127654</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6175</v>
+        <v>6442</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>497.2678476465268</v>
+        <v>612.7174042649226</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>71.8</v>
+        <v>1755</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>41.20216805687862</v>
+        <v>63.13050631345285</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>18.01158861274575</v>
+        <v>22.70195196824965</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.089274838727487</v>
+        <v>1.253271249720509</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.337533958252421</v>
+        <v>24.1232384107488</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6418</v>
+        <v>6419</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>494.9790454756463</v>
+        <v>607.4258108852572</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>33.25</v>
+        <v>155.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.89360194452969</v>
+        <v>52.9309624223672</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.08150143209632</v>
+        <v>18.59721663580844</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.310828913972597</v>
+        <v>0.5850697454560055</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>1</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0294273261626281</v>
+        <v>-1.42598678310628</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6419</v>
+        <v>6277</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>492.4258108852572</v>
+        <v>595.8755586367566</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>155.5</v>
+        <v>80.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.930962402678</v>
+        <v>52.20844337606324</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.59721666519543</v>
+        <v>29.10581051869469</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5850697454560055</v>
+        <v>0.4279629495064732</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.425986782762833</v>
+        <v>-0.4512570588114416</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6206</v>
+        <v>6416</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>490.3915436495319</v>
+        <v>572.2978961004479</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>138.5</v>
+        <v>100.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.84755950553028</v>
+        <v>53.46046863081191</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.59645105891802</v>
+        <v>13.13473239805396</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4412705860086925</v>
+        <v>0.8713115151236965</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.149638824270333</v>
+        <v>-0.3014324217671951</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6161</v>
+        <v>6207</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>488.6127924762631</v>
+        <v>558.8115294721562</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>51.6</v>
+        <v>111</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>52.68820440027039</v>
+        <v>52.14347091961502</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9.153623925935539</v>
+        <v>10.46229756600563</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6471164566813904</v>
+        <v>2.281005478993907</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.07444186891005219</v>
+        <v>1.295378268742495</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6183</v>
+        <v>6435</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>487.932833739293</v>
+        <v>558.1364248151053</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>246</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45.5128497227094</v>
+        <v>43.59652881078066</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25.72547004085123</v>
+        <v>13.66106401229797</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4119734973970658</v>
+        <v>0.3710273498593003</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.332253183671346</v>
+        <v>0.0196369732584251</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6217</v>
+        <v>6223</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>483.878701927643</v>
+        <v>551.5471780300628</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>188.5</v>
+        <v>5155</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.08629123239657</v>
+        <v>43.01049135533978</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18.58329487630525</v>
+        <v>17.3245229322651</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.937681443369062</v>
+        <v>0.4819506645294102</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>5.902063493878895</v>
+        <v>-27.77513110267259</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6274</v>
+        <v>6165</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>483.3819543220191</v>
+        <v>541.1384514368647</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1365</v>
+        <v>48.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>44.34725223258796</v>
+        <v>50.0806793252392</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.26967262202869</v>
+        <v>14.60312025896892</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.168661116026962</v>
+        <v>0.3132825013464269</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-21.17352115830523</v>
+        <v>0.1664490239914181</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6449</v>
+        <v>6230</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>482.1803561011046</v>
+        <v>536.6260462621817</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>237.5</v>
+        <v>110.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.65982240378568</v>
+        <v>50.16650514944148</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.22817556385561</v>
+        <v>12.99578682623714</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.253798536235634</v>
+        <v>0.9315698677400804</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.252199154188848</v>
+        <v>0.6084231829497975</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6204</v>
+        <v>6182</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>474.0938269924887</v>
+        <v>532.9832724220008</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>111</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.87770516202406</v>
+        <v>50.26438324185983</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.59314426916159</v>
+        <v>11.203936420689</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.087966141129599</v>
+        <v>0.5417054286224736</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>1</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.129728730765132</v>
+        <v>0.6540505354580721</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6269</v>
+        <v>6462</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>469.730618175258</v>
+        <v>515.7009809290165</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>67.7</v>
+        <v>101.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.61105946637142</v>
+        <v>52.33912140922529</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.09442916306549</v>
+        <v>10.46153497766178</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8233834463900674</v>
+        <v>1.229133420267916</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1118158164331446</v>
+        <v>0.4396684512886164</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6423</v>
+        <v>6170</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>464.1355088797334</v>
+        <v>510.9712711696054</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>85.40000000000001</v>
+        <v>48.45</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>64.30457691614762</v>
+        <v>56.74244218077229</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.54190925524893</v>
+        <v>19.12499586415403</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5826623741650099</v>
+        <v>0.9384612786231096</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.548847561730085</v>
+        <v>0.1024074515229644</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6442</v>
+        <v>6285</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>452.7174042649227</v>
+        <v>509.9631336046213</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1755</v>
+        <v>243.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>63.1305063019777</v>
+        <v>50.38497440302919</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.70195194889306</v>
+        <v>13.29558224503199</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.253271249720509</v>
+        <v>0.7128875990043481</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>24.12323841179844</v>
+        <v>0.5882009207460457</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6446</v>
+        <v>6198</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>448.3942849975497</v>
+        <v>504.2870396393925</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1310</v>
+        <v>19.75</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.98292448734222</v>
+        <v>51.86121623764508</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.20104966054231</v>
+        <v>6.708926975104275</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7895212834361595</v>
+        <v>0.1792145034846439</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-27.06100867754537</v>
+        <v>0.07839649528548159</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6265</v>
+        <v>6472</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>445.4646116773187</v>
+        <v>504.1298172700867</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>54.2</v>
+        <v>416</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46.37191577861052</v>
+        <v>46.72050970100339</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.89732933004015</v>
+        <v>24.20214844897268</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4012041825284339</v>
+        <v>0.2685511841744173</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.8508244509559437</v>
+        <v>-3.683574730565068</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6205</v>
+        <v>6206</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>440.3467540450373</v>
+        <v>500.3915436495319</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>138.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.29140461227618</v>
+        <v>49.8475595679496</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.16606290647407</v>
+        <v>18.59645110787067</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4316291301555115</v>
+        <v>0.4412705860086925</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.6726764923787661</v>
+        <v>-1.149638824842733</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6292</v>
+        <v>6175</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>439.044908638704</v>
+        <v>497.2678476465268</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>62</v>
+        <v>71.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.45449452384585</v>
+        <v>41.20216808900518</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.84468298715233</v>
+        <v>18.01158854547298</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4254359542765011</v>
+        <v>1.089274838727487</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>1</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.3304828241737845</v>
+        <v>0.337533958166567</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6192</v>
+        <v>6449</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>437.7832808377841</v>
+        <v>497.1803561011046</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>116.5</v>
+        <v>237.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.34050722336517</v>
+        <v>50.65982242264492</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.60189044401012</v>
+        <v>18.22817555875349</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7702374735031182</v>
+        <v>1.253798536235634</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.000666138328827</v>
+        <v>3.252199153902666</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6223</v>
+        <v>6418</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>436.547178030063</v>
+        <v>494.9790454756374</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>5155</v>
+        <v>33.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>43.01049136052547</v>
+        <v>49.89360193291412</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.3245229894432</v>
+        <v>28.0815014195334</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4819506645294102</v>
+        <v>0.310828913972597</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-27.77513110934981</v>
+        <v>-0.0294273260672295</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6284</v>
+        <v>6409</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>432.934094745824</v>
+        <v>494.7407872487714</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>965</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.08114209368545</v>
+        <v>43.18502222542658</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.16123621410274</v>
+        <v>16.91651895518318</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8993750268661912</v>
+        <v>0.6625498266867237</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.5672490639870527</v>
+        <v>-6.398650877238289</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6432</v>
+        <v>6191</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>430.0626543407314</v>
+        <v>489.5049713247768</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>60.9</v>
+        <v>82.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>38.63953775824132</v>
+        <v>43.04767177569884</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.20812248764354</v>
+        <v>23.58597965839168</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6755463565002964</v>
+        <v>0.5115204367840179</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.5724757184322451</v>
+        <v>0.3377067487177845</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6190</v>
+        <v>6274</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>429.882219261187</v>
+        <v>483.381954322019</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>68</v>
+        <v>1365</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.02225322784922</v>
+        <v>44.34725224119179</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.46786732711437</v>
+        <v>17.26967267647015</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.356404674683023</v>
+        <v>1.168661116026962</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4456798256814229</v>
+        <v>-21.17352115811441</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6230</v>
+        <v>6276</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>421.6260462621817</v>
+        <v>482.9183701468991</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>110.5</v>
+        <v>20.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.16650501194798</v>
+        <v>55.46484526009741</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12.99578680393288</v>
+        <v>17.92883283372115</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9315698677400804</v>
+        <v>0.6206907312472586</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.6084231836175795</v>
+        <v>0.1854817875210749</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6464</v>
+        <v>6269</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>418.5882667261833</v>
+        <v>469.730618175258</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.97623352392716</v>
+        <v>52.61105955417728</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>31.76659848075799</v>
+        <v>22.09442930431592</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2415955741151219</v>
+        <v>0.8233834463900674</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1439603254402289</v>
+        <v>0.1118158161469637</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6182</v>
+        <v>6246</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>417.9832724220008</v>
+        <v>462.8983697206609</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>111</v>
+        <v>12.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.26438323965628</v>
+        <v>50.75372615427073</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.20393640244516</v>
+        <v>25.7999609315987</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5417054286224736</v>
+        <v>0.2532812200232478</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>1</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.6540505354771682</v>
+        <v>0.1323447424114114</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6415</v>
+        <v>6166</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>416.4456081560063</v>
+        <v>451.9840718145236</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>428.5</v>
+        <v>121.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>44.6963382556484</v>
+        <v>47.40849593090905</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>9.457968733367506</v>
+        <v>16.61441166016321</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6095228821399423</v>
+        <v>1.485578704327344</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.605468202080498</v>
+        <v>-0.0433585625044683</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6174</v>
+        <v>6265</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>412.4438202833831</v>
+        <v>445.4646116773187</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>43.4</v>
+        <v>54.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.9207325191185</v>
+        <v>46.37191578211701</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.43823425884682</v>
+        <v>18.89732944050154</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2507087799103019</v>
+        <v>0.4012041825284339</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0512407983210053</v>
+        <v>-0.8508244509788345</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6257</v>
+        <v>6414</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>403.4676833132583</v>
+        <v>445.0071347055064</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.01438595050224</v>
+        <v>45.41000069390358</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.61740342885936</v>
+        <v>18.9244322985254</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8146932042657423</v>
+        <v>0.7184586881473494</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.804234248166741</v>
+        <v>-2.053969505059278</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6462</v>
+        <v>6205</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>400.7009809290165</v>
+        <v>440.3467540450373</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>101.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.33912130989402</v>
+        <v>53.29140466605264</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10.46153497349088</v>
+        <v>20.16606288919457</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.229133420267916</v>
+        <v>0.4316291301555115</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>1</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.4396684521471908</v>
+        <v>0.6726764921498105</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6210</v>
+        <v>6292</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>396.4866996536757</v>
+        <v>439.044908638704</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>17.75</v>
+        <v>62</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.45055545360628</v>
+        <v>54.454494507667</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>8.546891928864222</v>
+        <v>24.84468298715233</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5997768493020607</v>
+        <v>0.4254359542765011</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0152225109326586</v>
+        <v>-0.3304828241356234</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6220</v>
+        <v>6192</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>395.8327090304476</v>
+        <v>437.7832808377841</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>25.8</v>
+        <v>116.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>42.63896773699469</v>
+        <v>50.3405073202626</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.96522836965225</v>
+        <v>15.60189049821864</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.070083005710807</v>
+        <v>0.7702374735031182</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2376212316283804</v>
+        <v>0.0006661380235609</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6411</v>
+        <v>6284</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>395.6982661463967</v>
+        <v>432.934094745824</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>80.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.28214668415188</v>
+        <v>50.08114212489523</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11.32688647325343</v>
+        <v>13.16123621051283</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7262064049484411</v>
+        <v>0.8993750268661912</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.5793676009300424</v>
+        <v>0.5672490637962679</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6241</v>
+        <v>6432</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>391.4054287962657</v>
+        <v>430.0626543407314</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>16.75</v>
+        <v>60.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.48254872565077</v>
+        <v>38.63953775039509</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.29540259770143</v>
+        <v>15.20812251453739</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1985766616919718</v>
+        <v>0.6755463565002964</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1016548505066832</v>
+        <v>-0.5724757184704052</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6198</v>
+        <v>6190</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>389.2870396393924</v>
+        <v>429.8822192611873</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>19.75</v>
+        <v>68</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.86121586626668</v>
+        <v>48.02225323459943</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6.708926074529018</v>
+        <v>18.46786730735933</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1792145034846439</v>
+        <v>1.356404674683023</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.07839650136228669</v>
+        <v>0.4456798255287899</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6237</v>
+        <v>6464</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>387.641876076807</v>
+        <v>418.5882667261833</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>35.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.16044302641636</v>
+        <v>46.97623353515272</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.68507604882994</v>
+        <v>31.76659862614036</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9296707922094402</v>
+        <v>0.2415955741151219</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.4104920453430555</v>
+        <v>-0.1439603254402289</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6234</v>
+        <v>6415</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>386.5913584247046</v>
+        <v>416.4456081560064</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>34.2</v>
+        <v>428.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.26530416367328</v>
+        <v>44.69633825104541</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.21950892273449</v>
+        <v>9.457968770609687</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9522851078807923</v>
+        <v>0.6095228821399423</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0376623263696125</v>
+        <v>-1.605468202462088</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6409</v>
+        <v>6174</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>379.7407872487714</v>
+        <v>412.4438202833831</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>965</v>
+        <v>43.4</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.18502220722982</v>
+        <v>45.92073251552451</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.91651893116933</v>
+        <v>13.43823411748573</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6625498266867237</v>
+        <v>0.2507087799103019</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-6.398650875330416</v>
+        <v>0.0512407983114655</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6474</v>
+        <v>6235</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>377.9274446303224</v>
+        <v>409.502165506957</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>36.55</v>
+        <v>39.45</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.59663828686494</v>
+        <v>53.53931257460091</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.09030347087779</v>
+        <v>11.04545721617731</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1211095410193869</v>
+        <v>0.6869881789782017</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.376888543206639</v>
+        <v>0.2202347875182284</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6243</v>
+        <v>6417</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>377.8612931739795</v>
+        <v>406.1985832380543</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>39.4</v>
+        <v>108</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>40.34939287799788</v>
+        <v>44.24492736428021</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.93452747234788</v>
+        <v>27.7639109413769</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2611747645224622</v>
+        <v>0.7923011583175974</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.4614627353608904</v>
+        <v>0.3863857836198701</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6191</v>
+        <v>6257</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>374.5049713247768</v>
+        <v>403.4676833132583</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>82.5</v>
+        <v>212</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.04767159020611</v>
+        <v>52.01438596325813</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.58597964906431</v>
+        <v>13.6174035414859</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5115204367840179</v>
+        <v>0.8146932042657423</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3377067492710948</v>
+        <v>1.804234248109485</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6277</v>
+        <v>6210</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>370.8755586367566</v>
+        <v>396.4866996536757</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>80.3</v>
+        <v>17.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.2084433527592</v>
+        <v>51.45055548699992</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.105810497205</v>
+        <v>8.546892068507345</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4279629495064732</v>
+        <v>0.5997768493020607</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.4512570587351185</v>
+        <v>-0.0152225110089768</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6276</v>
+        <v>6220</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>367.918370146899</v>
+        <v>395.8327090304476</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.7</v>
+        <v>25.8</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>55.46484460421507</v>
+        <v>42.63896775864507</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.92883295154068</v>
+        <v>15.96522835389085</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6206907312472586</v>
+        <v>1.070083005710807</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1854817878645038</v>
+        <v>0.2376212316760806</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6164</v>
+        <v>6411</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>353.1325557856808</v>
+        <v>395.6982661463967</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11.95</v>
+        <v>80.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.56165919933242</v>
+        <v>50.28214671770351</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.42051554596006</v>
+        <v>11.32688648856464</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7045975368441578</v>
+        <v>0.7262064049484411</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.036929877415906</v>
+        <v>0.5793676008918924</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6259</v>
+        <v>6241</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>352.9167805604779</v>
+        <v>391.4054287962657</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30.15</v>
+        <v>16.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.35897326226274</v>
+        <v>54.4825487491168</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9.814774296698818</v>
+        <v>22.29540260381392</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.681443884984219</v>
+        <v>0.1985766616919718</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0330923500134699</v>
+        <v>0.1016548504506157</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6165</v>
+        <v>6470</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>351.1384514368646</v>
+        <v>389.2192476725205</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>48.9</v>
+        <v>41.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.08067907401806</v>
+        <v>36.81325831706672</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.60312018101525</v>
+        <v>40.12215687628934</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3132825013464269</v>
+        <v>0.678179250873057</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1664490241822159</v>
+        <v>0.2183469701496794</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6405</v>
+        <v>6237</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>348.2039542211116</v>
+        <v>387.641876076807</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>40.1</v>
+        <v>35.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.59339034735267</v>
+        <v>50.16044305973227</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21.75657131655354</v>
+        <v>20.68507614524049</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.249077781640378</v>
+        <v>0.9296707922094402</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.5868995000097252</v>
+        <v>0.4104920452190398</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6208</v>
+        <v>6234</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>346.719679283793</v>
+        <v>386.5913584247047</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>74.2</v>
+        <v>34.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>25.76642882274474</v>
+        <v>41.26530420134785</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.34262300765921</v>
+        <v>19.21950899852721</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.802861382534928</v>
+        <v>0.9522851078807923</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.4672262238543407</v>
+        <v>0.0376623263028335</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6456</v>
+        <v>6474</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>338.7714188263469</v>
+        <v>377.9274446303223</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>68.8</v>
+        <v>36.55</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.9208955509645</v>
+        <v>40.59663805626379</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.95766528328024</v>
+        <v>14.09030348774741</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3714398935094631</v>
+        <v>0.1211095410193869</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0389523924314154</v>
+        <v>-0.3768885429395225</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6245</v>
+        <v>6243</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>335.9790487820948</v>
+        <v>377.8612931739795</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>78.2</v>
+        <v>39.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.41488411676978</v>
+        <v>40.34939288028095</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.90344411013727</v>
+        <v>21.93452750149737</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5636937988275083</v>
+        <v>0.2611747645224622</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.7637577859981057</v>
+        <v>-0.4614627353418079</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6414</v>
+        <v>6164</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>330.0071347055064</v>
+        <v>353.1325557856808</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>395</v>
+        <v>11.95</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.41000066636912</v>
+        <v>45.56165921169988</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.92443231337896</v>
+        <v>16.42051557679644</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7184586881473494</v>
+        <v>0.7045975368441578</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-2.053969504868484</v>
+        <v>0.0369298773968269</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6163</v>
+        <v>6259</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>328.9479299568561</v>
+        <v>352.9167805604779</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>41.2</v>
+        <v>30.15</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.54764818576997</v>
+        <v>47.35897323812827</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.78769930543422</v>
+        <v>9.814774238413916</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2946116424619589</v>
+        <v>0.681443884984219</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.074661074829111</v>
+        <v>0.0330923500611678</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6246</v>
+        <v>6185</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>322.8983697206609</v>
+        <v>351.1196551706891</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>12.8</v>
+        <v>12.75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.75372613533138</v>
+        <v>35.96720642398451</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25.79996086468578</v>
+        <v>25.5153673092729</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2532812200232478</v>
+        <v>0.4477172349179295</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1323447424304885</v>
+        <v>0.0081563821488644</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6184</v>
+        <v>6405</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>321.4975044760236</v>
+        <v>348.2039542211116</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>17.25039381899751</v>
+        <v>47.59339037036679</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>36.52176874294564</v>
+        <v>21.75657133586387</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.259630965279687</v>
+        <v>1.249077781640378</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0951421370247541</v>
+        <v>0.5868995000001798</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6244</v>
+        <v>6208</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>300.7515005073727</v>
+        <v>346.719679283793</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>23.4</v>
+        <v>74.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.03060778329046</v>
+        <v>25.76642884732999</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.15451189192863</v>
+        <v>11.34262303619189</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6795613914736579</v>
+        <v>1.802861382534928</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1059104198885755</v>
+        <v>-0.4672262237971063</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6279</v>
+        <v>6184</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>297.7384367946008</v>
+        <v>341.4975044760242</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>117.5</v>
+        <v>40.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>35.05722215333408</v>
+        <v>17.25039389243526</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.88118758988777</v>
+        <v>36.5217687297625</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6188159507076474</v>
+        <v>2.259630965279687</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.323567810408324</v>
+        <v>-0.0951421370629101</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6216</v>
+        <v>6456</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>296.3455201125347</v>
+        <v>338.7714188263469</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>20.5</v>
+        <v>68.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>28.71422948315897</v>
+        <v>51.92089565517097</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.35995919116236</v>
+        <v>15.95766529336852</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8417254784511126</v>
+        <v>0.3714398935094631</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1473773324813244</v>
+        <v>0.0389523922787817</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6235</v>
+        <v>6245</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>294.502165506957</v>
+        <v>335.9790487820951</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>39.45</v>
+        <v>78.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.53931243893896</v>
+        <v>42.41488417402206</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.04545720523859</v>
+        <v>13.90344413943208</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6869881789782017</v>
+        <v>0.5636937988275083</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2202347876613239</v>
+        <v>-0.7637577862079735</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6417</v>
+        <v>6163</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>291.1985832380542</v>
+        <v>328.9479299568561</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>108</v>
+        <v>41.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.24492707973045</v>
+        <v>45.54764822672446</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.76391101366771</v>
+        <v>13.78769927471107</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7923011583175974</v>
+        <v>0.2946116424619589</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.3863857836198701</v>
+        <v>-0.0746610748672701</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6443</v>
+        <v>6215</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>278.7556849472266</v>
+        <v>324.5174445875186</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.95</v>
+        <v>99</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.82446761024381</v>
+        <v>49.49504136863597</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.89198357859231</v>
+        <v>12.48302528379965</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8127530270156385</v>
+        <v>0.4914563007485866</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0227463067856951</v>
+        <v>0.1300075653268503</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6470</v>
+        <v>6244</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>274.2192476725205</v>
+        <v>300.7515005073725</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.8</v>
+        <v>23.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.81325813564053</v>
+        <v>42.03060782596711</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>40.1221568389199</v>
+        <v>13.1545118526939</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.678179250873057</v>
+        <v>0.6795613914736579</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>1</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.2183469703023106</v>
+        <v>-0.1059104199935134</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6282</v>
+        <v>6279</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>269.453606933044</v>
+        <v>297.7384367946008</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>44</v>
+        <v>117.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.08040495437056</v>
+        <v>35.05722229389245</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.50430050933062</v>
+        <v>16.88118753534781</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5943946725710394</v>
+        <v>0.6188159507076474</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0778007813508181</v>
+        <v>-1.323567811362293</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6239</v>
+        <v>6216</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>266.6963174734349</v>
+        <v>296.3455201125348</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>276.5</v>
+        <v>20.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.64768914692769</v>
+        <v>28.71422958759386</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9.324719841808417</v>
+        <v>24.35995921899629</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6734291679633279</v>
+        <v>0.8417254784511126</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.286646808978601</v>
+        <v>-0.1473773325671833</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6412</v>
+        <v>6443</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>266.5752440699758</v>
+        <v>278.7556849472266</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>24.95</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>40.96782400977147</v>
+        <v>38.82446760707614</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.23034813775434</v>
+        <v>14.89198364565107</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.133200859979711</v>
+        <v>0.8127530270156385</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.2680956606356939</v>
+        <v>0.0227463067761555</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6176</v>
+        <v>6203</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>252.6618053615616</v>
+        <v>273.123858069684</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>53.23900068185799</v>
+        <v>45.04901030033999</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.91360107703864</v>
+        <v>13.71037133010945</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3273250916221636</v>
+        <v>0.3068772926487117</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.2263989198952427</v>
+        <v>0.305461707340297</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6227</v>
+        <v>6282</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>251.0782544720475</v>
+        <v>269.453606933044</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>113.5</v>
+        <v>44</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,49 +5428,49 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.7128895960272</v>
+        <v>41.08040496663074</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8.546363398058427</v>
+        <v>16.50430043357552</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4044362062460833</v>
+        <v>0.5943946725710394</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.8459225361600737</v>
+        <v>0.0778007813508181</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6283</v>
+        <v>6412</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>244.6600577940598</v>
+        <v>266.5752440699758</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>20.05</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,25 +5481,25 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.93266896807495</v>
+        <v>40.96782406829901</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>23.64310812043334</v>
+        <v>21.23034814971964</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7229121296250117</v>
+        <v>1.133200859979711</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.08182695936667191</v>
+        <v>0.2680956605403004</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6194</v>
+        <v>6239</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>244.6480207012974</v>
+        <v>256.6963174734349</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>29.65</v>
+        <v>276.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.39025062439709</v>
+        <v>49.64768914359768</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.24415478679738</v>
+        <v>9.324719976219766</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2294106750923839</v>
+        <v>0.6734291679633279</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0725046544466789</v>
+        <v>1.286646809073985</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6270</v>
+        <v>6176</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>239.0367041393953</v>
+        <v>252.6618053615616</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>28.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.80450124542539</v>
+        <v>53.23900062852559</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.611355547042551</v>
+        <v>23.91360128920497</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4762507407966986</v>
+        <v>0.3273250916221636</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>1</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0338841262281586</v>
+        <v>0.2263989203857206</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6166</v>
+        <v>6227</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>236.9840718145234</v>
+        <v>251.0782544720474</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>121.5</v>
+        <v>113.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.40849591155214</v>
+        <v>44.71288962546657</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.61441168515115</v>
+        <v>8.546363398058428</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.485578704327344</v>
+        <v>0.4044362062460833</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0433585623899794</v>
+        <v>-0.8459225364653518</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6185</v>
+        <v>6283</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>236.1196551706892</v>
+        <v>244.6600577940598</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>12.75</v>
+        <v>20.05</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>35.96720644967471</v>
+        <v>43.93266927292364</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>25.51536730709606</v>
+        <v>23.64310816858574</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4477172349179295</v>
+        <v>0.7229121296250117</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.008156382139324399</v>
+        <v>0.0818269592521953</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6451</v>
+        <v>6194</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>230.4857185419912</v>
+        <v>244.6480207012974</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>449</v>
+        <v>29.65</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.7315157612228</v>
+        <v>42.39025127870028</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.04341634127063</v>
+        <v>23.24415482236627</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9976231687744528</v>
+        <v>0.2294106750923839</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>4.929473143594516</v>
+        <v>0.07250465438944111</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6229</v>
+        <v>6189</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>227.5305692160595</v>
+        <v>244.5354518653442</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>23.65</v>
+        <v>48.15</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.44801376547391</v>
+        <v>47.27969544710621</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.30232926822477</v>
+        <v>6.180670832647008</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6047846693402209</v>
+        <v>0.7547075529534267</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0581978783561207</v>
+        <v>0.0264541603680153</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>221.8133771214121</v>
+        <v>239.0367041393953</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>24.75</v>
+        <v>28.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.03676036329135</v>
+        <v>39.80450125623361</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.67020897122067</v>
+        <v>9.611355541657495</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.397413063701086</v>
+        <v>0.4762507407966986</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0290421063860661</v>
+        <v>-0.0338841262567802</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6261</v>
+        <v>6451</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>209.7360756814826</v>
+        <v>230.4857185419912</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>449</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.9636689132908</v>
+        <v>50.7315157797926</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.25154085774225</v>
+        <v>11.04341638020245</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.159591023762597</v>
+        <v>0.9976231687744528</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.4755312489230432</v>
+        <v>4.929473143117516</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6215</v>
+        <v>6229</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>209.5174445875186</v>
+        <v>227.5305692160595</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>99</v>
+        <v>23.65</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.49504132159971</v>
+        <v>46.44801362171534</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.48302530626224</v>
+        <v>12.30232924515717</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4914563007485866</v>
+        <v>0.6047846693402209</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1300075655367298</v>
+        <v>0.0581978784038202</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6465</v>
+        <v>6266</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>208.4889340808193</v>
+        <v>221.8133771214121</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>46</v>
+        <v>24.75</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.17781733350211</v>
+        <v>45.03676043945164</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.28825705897056</v>
+        <v>13.67020889890367</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4835620859887272</v>
+        <v>1.397413063701086</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3404112931446157</v>
+        <v>-0.0290421064337655</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6188</v>
+        <v>6261</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>205.1198050186562</v>
+        <v>209.7360756814826</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.68553500985801</v>
+        <v>45.96366892810364</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.99791529558923</v>
+        <v>18.251540900502</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5509095020205073</v>
+        <v>1.159591023762597</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0712342659166505</v>
+        <v>0.4755312488467269</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6201</v>
+        <v>6465</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>200.8841155260899</v>
+        <v>208.4889340808193</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>44.55</v>
+        <v>46</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>35.84162316642465</v>
+        <v>40.17781732443623</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.048366040011</v>
+        <v>12.28825703845566</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.177300675335148</v>
+        <v>0.4835620859887272</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.08765468984824509</v>
+        <v>0.3404112930628677</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6233</v>
+        <v>6188</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>166.5877408790826</v>
+        <v>205.1198050186582</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>20.85</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.99240615368515</v>
+        <v>39.6855351182862</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.46475446906161</v>
+        <v>18.99791526830989</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6957750318211372</v>
+        <v>0.5509095020205073</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0250456336748512</v>
+        <v>-0.0712342662409972</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6203</v>
+        <v>6201</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>158.1238580696841</v>
+        <v>200.8841155260899</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>60.7</v>
+        <v>44.55</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.04901028755977</v>
+        <v>35.84162331445692</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.71037132551001</v>
+        <v>26.04836607349478</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3068772926487117</v>
+        <v>1.177300675335148</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.3054617072639787</v>
+        <v>0.08765468984824509</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6222</v>
+        <v>6233</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>154.0764582323877</v>
+        <v>166.5877408790826</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>20</v>
+        <v>20.85</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>51.25412551161826</v>
+        <v>40.99240620380091</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.692920411336804</v>
+        <v>12.46475449354137</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.257735070684711</v>
+        <v>0.6957750318211372</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2412122246903164</v>
+        <v>0.0250456336462339</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6281</v>
+        <v>6222</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>147.5953574376994</v>
+        <v>154.0764582323877</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>51.4</v>
+        <v>20</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.06054706714083</v>
+        <v>51.25412549640501</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.6595835957181</v>
+        <v>6.692920411336806</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.498917313724092</v>
+        <v>1.257735070684711</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0171835562357569</v>
+        <v>0.2412122246903164</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6189</v>
+        <v>6281</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>134.5354518653442</v>
+        <v>147.5953574376996</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>48.15</v>
+        <v>51.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.27969534393824</v>
+        <v>48.06054686550056</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6.180670741643365</v>
+        <v>10.65958364368142</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7547075529534267</v>
+        <v>1.498917313724092</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0264541604061768</v>
+        <v>-0.0171835561403521</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>47.56300579493043</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8.490191910852406</v>
+        <v>8.490191839497832</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>106.4402748356505</v>
+        <v>106.4402748356504</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>10.2</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.71384000344685</v>
+        <v>37.71384009818117</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.06395348557786</v>
+        <v>11.06395335887871</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.290711931132078</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0130047360084395</v>
+        <v>-0.0130047361065372</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>97.43438921854468</v>
+        <v>97.43438921854472</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.24634457418925</v>
+        <v>39.24634456944286</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.483973740253</v>
+        <v>12.48397377762736</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.037887619491723</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-1.574576521207119</v>
+        <v>-1.574576521235738</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.6731518684301</v>
+        <v>43.67315184505794</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.18701212963874</v>
+        <v>16.18701212244297</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.2748184264688713</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.06916288893797411</v>
+        <v>-0.069162889014293</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
